--- a/BOM/Client-BOM-IoT-Button.xlsx
+++ b/BOM/Client-BOM-IoT-Button.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="2 Boards" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="233">
   <si>
     <t>Component list</t>
   </si>
@@ -701,9 +701,6 @@
   </si>
   <si>
     <t>CC0603KRX7R8BB102</t>
-  </si>
-  <si>
-    <t>Vlaue</t>
   </si>
   <si>
     <t>Quantity (5 Boards)</t>
@@ -1238,15 +1235,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1276,6 +1264,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1680,11 +1677,12 @@
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="29.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1696,10 +1694,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1710,7 +1708,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -1728,14 +1726,14 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="55"/>
+      <c r="L3" s="65"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1746,14 +1744,14 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="56"/>
+      <c r="L4" s="66"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1771,7 +1769,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="56"/>
+      <c r="L5" s="66"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1785,7 +1783,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="56"/>
+      <c r="L6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1799,7 +1797,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="56"/>
+      <c r="L7" s="66"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1813,7 +1811,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="56"/>
+      <c r="L8" s="66"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1839,25 +1837,25 @@
         <v>179</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="J9" s="29" t="s">
         <v>222</v>
       </c>
       <c r="K9" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="L9" s="29" t="s">
         <v>229</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="57">
+      <c r="B10" s="54">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="36" t="s">
@@ -1889,11 +1887,11 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="59">
+      <c r="B11" s="56">
         <f t="shared" ref="B11:B53" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="38" t="s">
@@ -1925,11 +1923,11 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="57">
+      <c r="B12" s="54">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="36" t="s">
@@ -1961,11 +1959,11 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="59">
+      <c r="B13" s="56">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="38" t="s">
@@ -1997,11 +1995,11 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="57">
+      <c r="B14" s="54">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="36" t="s">
@@ -2033,11 +2031,11 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="59">
+      <c r="B15" s="56">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="38" t="s">
@@ -2069,11 +2067,11 @@
     </row>
     <row r="16" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="57">
+      <c r="B16" s="54">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="36" t="s">
@@ -2105,11 +2103,11 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="59">
+      <c r="B17" s="56">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="38" t="s">
@@ -2141,11 +2139,11 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="57">
+      <c r="B18" s="54">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="36" t="s">
@@ -2177,11 +2175,11 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="59">
+      <c r="B19" s="56">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="38" t="s">
@@ -2213,11 +2211,11 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="57">
+      <c r="B20" s="54">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="55" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="36" t="s">
@@ -2249,11 +2247,11 @@
     </row>
     <row r="21" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="59">
+      <c r="B21" s="56">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="58" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="38" t="s">
@@ -2285,11 +2283,11 @@
     </row>
     <row r="22" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="57">
+      <c r="B22" s="54">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="55" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="36" t="s">
@@ -2321,11 +2319,11 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="59">
+      <c r="B23" s="56">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="58" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="38" t="s">
@@ -2357,11 +2355,11 @@
     </row>
     <row r="24" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="57">
+      <c r="B24" s="54">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="55" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="36" t="s">
@@ -2393,11 +2391,11 @@
     </row>
     <row r="25" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="59">
+      <c r="B25" s="56">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="58" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="38" t="s">
@@ -2429,11 +2427,11 @@
     </row>
     <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="57">
+      <c r="B26" s="54">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="55" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="36" t="s">
@@ -2465,11 +2463,11 @@
     </row>
     <row r="27" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="59">
+      <c r="B27" s="56">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="58" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="38" t="s">
@@ -2501,11 +2499,11 @@
     </row>
     <row r="28" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="57">
+      <c r="B28" s="54">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="55" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="36" t="s">
@@ -2537,11 +2535,11 @@
     </row>
     <row r="29" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="59">
+      <c r="B29" s="56">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="58" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="38" t="s">
@@ -2573,11 +2571,11 @@
     </row>
     <row r="30" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="57">
+      <c r="B30" s="54">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="55" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="36" t="s">
@@ -2609,11 +2607,11 @@
     </row>
     <row r="31" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="59">
+      <c r="B31" s="56">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="58" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="38" t="s">
@@ -2645,11 +2643,11 @@
     </row>
     <row r="32" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="57">
+      <c r="B32" s="54">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" s="55" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="36" t="s">
@@ -2681,26 +2679,26 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="59">
+      <c r="B33" s="56">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="60" t="s">
+      <c r="E33" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="F33" s="60" t="s">
+      <c r="F33" s="57" t="s">
         <v>223</v>
       </c>
-      <c r="G33" s="60" t="s">
+      <c r="G33" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="H33" s="60" t="s">
+      <c r="H33" s="57" t="s">
         <v>224</v>
       </c>
       <c r="I33" s="37" t="s">
@@ -2717,11 +2715,11 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="57">
+      <c r="B34" s="54">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="55" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="36" t="s">
@@ -2753,11 +2751,11 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="59">
+      <c r="B35" s="56">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="61" t="s">
+      <c r="C35" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="38" t="s">
@@ -2789,11 +2787,11 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="57">
+      <c r="B36" s="54">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="61" t="s">
+      <c r="C36" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D36" s="36" t="s">
@@ -2825,11 +2823,11 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="59">
+      <c r="B37" s="56">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D37" s="38" t="s">
@@ -2861,11 +2859,11 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="57">
+      <c r="B38" s="54">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="36" t="s">
@@ -2897,11 +2895,11 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="59">
+      <c r="B39" s="56">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="38" t="s">
@@ -2933,11 +2931,11 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="57">
+      <c r="B40" s="54">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="C40" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="36" t="s">
@@ -2969,11 +2967,11 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="59">
+      <c r="B41" s="56">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="61" t="s">
+      <c r="C41" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="38" t="s">
@@ -3005,26 +3003,26 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="62">
+      <c r="B42" s="59">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="63" t="s">
+      <c r="C42" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="64" t="s">
+      <c r="D42" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="E42" s="64" t="s">
+      <c r="E42" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="64" t="s">
+      <c r="F42" s="61" t="s">
         <v>135</v>
       </c>
-      <c r="G42" s="64" t="s">
+      <c r="G42" s="61" t="s">
         <v>169</v>
       </c>
-      <c r="H42" s="64" t="s">
+      <c r="H42" s="61" t="s">
         <v>180</v>
       </c>
       <c r="I42" s="37" t="s">
@@ -3041,11 +3039,11 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="59">
+      <c r="B43" s="56">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D43" s="38" t="s">
@@ -3077,11 +3075,11 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="57">
+      <c r="B44" s="54">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="61" t="s">
+      <c r="C44" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D44" s="36" t="s">
@@ -3113,11 +3111,11 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="59">
+      <c r="B45" s="56">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D45" s="38" t="s">
@@ -3149,11 +3147,11 @@
     </row>
     <row r="46" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="57">
+      <c r="B46" s="54">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="58" t="s">
+      <c r="C46" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D46" s="36" t="s">
@@ -3185,11 +3183,11 @@
     </row>
     <row r="47" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
-      <c r="B47" s="59">
+      <c r="B47" s="56">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="58" t="s">
         <v>22</v>
       </c>
       <c r="D47" s="38" t="s">
@@ -3221,11 +3219,11 @@
     </row>
     <row r="48" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="57">
+      <c r="B48" s="54">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="61" t="s">
+      <c r="C48" s="58" t="s">
         <v>22</v>
       </c>
       <c r="D48" s="36" t="s">
@@ -3257,11 +3255,11 @@
     </row>
     <row r="49" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="59">
+      <c r="B49" s="56">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="58" t="s">
         <v>19</v>
       </c>
       <c r="D49" s="38" t="s">
@@ -3293,11 +3291,11 @@
     </row>
     <row r="50" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="57">
+      <c r="B50" s="54">
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D50" s="36" t="s">
@@ -3329,11 +3327,11 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="59">
+      <c r="B51" s="56">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C51" s="58" t="s">
         <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
@@ -3365,11 +3363,11 @@
     </row>
     <row r="52" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="57">
+      <c r="B52" s="54">
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="36" t="s">
@@ -3401,11 +3399,11 @@
     </row>
     <row r="53" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="59">
+      <c r="B53" s="56">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="61" t="s">
+      <c r="C53" s="58" t="s">
         <v>23</v>
       </c>
       <c r="D53" s="38" t="s">
@@ -3437,11 +3435,11 @@
     </row>
     <row r="54" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
-      <c r="B54" s="57">
+      <c r="B54" s="54">
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="C54" s="55" t="s">
         <v>24</v>
       </c>
       <c r="D54" s="36" t="s">
@@ -3537,10 +3535,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3551,7 +3549,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
@@ -3569,14 +3567,14 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="55"/>
+      <c r="L3" s="65"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3587,14 +3585,14 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="56"/>
+      <c r="L4" s="66"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3612,7 +3610,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="56"/>
+      <c r="L5" s="66"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -3626,7 +3624,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="56"/>
+      <c r="L6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -3640,7 +3638,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="56"/>
+      <c r="L7" s="66"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3654,7 +3652,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="56"/>
+      <c r="L8" s="66"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3680,25 +3678,25 @@
         <v>179</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J9" s="29" t="s">
         <v>222</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
-      <c r="B10" s="57">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="62"/>
+      <c r="B10" s="54">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="36" t="s">
@@ -3728,13 +3726,13 @@
       </c>
       <c r="L10" s="36"/>
     </row>
-    <row r="11" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="65"/>
-      <c r="B11" s="59">
+    <row r="11" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="62"/>
+      <c r="B11" s="56">
         <f t="shared" ref="B11:B53" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="38" t="s">
@@ -3764,13 +3762,13 @@
       </c>
       <c r="L11" s="38"/>
     </row>
-    <row r="12" spans="1:12" s="66" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="65"/>
-      <c r="B12" s="57">
+    <row r="12" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="62"/>
+      <c r="B12" s="54">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="36" t="s">
@@ -3800,13 +3798,13 @@
       </c>
       <c r="L12" s="36"/>
     </row>
-    <row r="13" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="65"/>
-      <c r="B13" s="59">
+    <row r="13" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="62"/>
+      <c r="B13" s="56">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="38" t="s">
@@ -3836,13 +3834,13 @@
       </c>
       <c r="L13" s="38"/>
     </row>
-    <row r="14" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="65"/>
-      <c r="B14" s="57">
+    <row r="14" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="62"/>
+      <c r="B14" s="54">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="36" t="s">
@@ -3872,13 +3870,13 @@
       </c>
       <c r="L14" s="36"/>
     </row>
-    <row r="15" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="65"/>
-      <c r="B15" s="59">
+    <row r="15" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="62"/>
+      <c r="B15" s="56">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="38" t="s">
@@ -3908,13 +3906,13 @@
       </c>
       <c r="L15" s="38"/>
     </row>
-    <row r="16" spans="1:12" s="66" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A16" s="65"/>
-      <c r="B16" s="57">
+    <row r="16" spans="1:12" s="63" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A16" s="62"/>
+      <c r="B16" s="54">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="36" t="s">
@@ -3944,13 +3942,13 @@
       </c>
       <c r="L16" s="36"/>
     </row>
-    <row r="17" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="65"/>
-      <c r="B17" s="59">
+    <row r="17" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="62"/>
+      <c r="B17" s="56">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="38" t="s">
@@ -3980,13 +3978,13 @@
       </c>
       <c r="L17" s="38"/>
     </row>
-    <row r="18" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="65"/>
-      <c r="B18" s="57">
+    <row r="18" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="62"/>
+      <c r="B18" s="54">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="55" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="36" t="s">
@@ -4016,13 +4014,13 @@
       </c>
       <c r="L18" s="36"/>
     </row>
-    <row r="19" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="65"/>
-      <c r="B19" s="59">
+    <row r="19" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="62"/>
+      <c r="B19" s="56">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="58" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="38" t="s">
@@ -4052,13 +4050,13 @@
       </c>
       <c r="L19" s="38"/>
     </row>
-    <row r="20" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="65"/>
-      <c r="B20" s="57">
+    <row r="20" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="62"/>
+      <c r="B20" s="54">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="55" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="36" t="s">
@@ -4088,13 +4086,13 @@
       </c>
       <c r="L20" s="36"/>
     </row>
-    <row r="21" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A21" s="65"/>
-      <c r="B21" s="59">
+    <row r="21" spans="1:12" s="63" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A21" s="62"/>
+      <c r="B21" s="56">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="58" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="38" t="s">
@@ -4124,13 +4122,13 @@
       </c>
       <c r="L21" s="38"/>
     </row>
-    <row r="22" spans="1:12" s="66" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A22" s="65"/>
-      <c r="B22" s="57">
+    <row r="22" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="62"/>
+      <c r="B22" s="54">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="55" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="36" t="s">
@@ -4160,13 +4158,13 @@
       </c>
       <c r="L22" s="36"/>
     </row>
-    <row r="23" spans="1:12" s="66" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A23" s="65"/>
-      <c r="B23" s="59">
+    <row r="23" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="62"/>
+      <c r="B23" s="56">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="58" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="38" t="s">
@@ -4196,13 +4194,13 @@
       </c>
       <c r="L23" s="38"/>
     </row>
-    <row r="24" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A24" s="65"/>
-      <c r="B24" s="57">
+    <row r="24" spans="1:12" s="63" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A24" s="62"/>
+      <c r="B24" s="54">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="55" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="36" t="s">
@@ -4232,13 +4230,13 @@
       </c>
       <c r="L24" s="36"/>
     </row>
-    <row r="25" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A25" s="65"/>
-      <c r="B25" s="59">
+    <row r="25" spans="1:12" s="63" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A25" s="62"/>
+      <c r="B25" s="56">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="58" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="38" t="s">
@@ -4268,13 +4266,13 @@
       </c>
       <c r="L25" s="38"/>
     </row>
-    <row r="26" spans="1:12" s="66" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A26" s="65"/>
-      <c r="B26" s="57">
+    <row r="26" spans="1:12" s="63" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A26" s="62"/>
+      <c r="B26" s="54">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="55" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="36" t="s">
@@ -4304,13 +4302,13 @@
       </c>
       <c r="L26" s="36"/>
     </row>
-    <row r="27" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A27" s="65"/>
-      <c r="B27" s="59">
+    <row r="27" spans="1:12" s="63" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A27" s="62"/>
+      <c r="B27" s="56">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="58" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="38" t="s">
@@ -4340,13 +4338,13 @@
       </c>
       <c r="L27" s="38"/>
     </row>
-    <row r="28" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A28" s="65"/>
-      <c r="B28" s="57">
+    <row r="28" spans="1:12" s="63" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A28" s="62"/>
+      <c r="B28" s="54">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="55" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="36" t="s">
@@ -4376,13 +4374,13 @@
       </c>
       <c r="L28" s="36"/>
     </row>
-    <row r="29" spans="1:12" s="66" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="65"/>
-      <c r="B29" s="59">
+    <row r="29" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A29" s="62"/>
+      <c r="B29" s="56">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="58" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="38" t="s">
@@ -4412,13 +4410,13 @@
       </c>
       <c r="L29" s="38"/>
     </row>
-    <row r="30" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A30" s="65"/>
-      <c r="B30" s="57">
+    <row r="30" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A30" s="62"/>
+      <c r="B30" s="54">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="55" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="36" t="s">
@@ -4448,13 +4446,13 @@
       </c>
       <c r="L30" s="36"/>
     </row>
-    <row r="31" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A31" s="65"/>
-      <c r="B31" s="59">
+    <row r="31" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="62"/>
+      <c r="B31" s="56">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="58" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="38" t="s">
@@ -4484,13 +4482,13 @@
       </c>
       <c r="L31" s="38"/>
     </row>
-    <row r="32" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A32" s="65"/>
-      <c r="B32" s="57">
+    <row r="32" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="62"/>
+      <c r="B32" s="54">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" s="55" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="36" t="s">
@@ -4520,28 +4518,28 @@
       </c>
       <c r="L32" s="36"/>
     </row>
-    <row r="33" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="65"/>
-      <c r="B33" s="59">
+    <row r="33" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="62"/>
+      <c r="B33" s="56">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="60" t="s">
+      <c r="E33" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="F33" s="60" t="s">
+      <c r="F33" s="57" t="s">
         <v>223</v>
       </c>
-      <c r="G33" s="60" t="s">
+      <c r="G33" s="57" t="s">
         <v>133</v>
       </c>
-      <c r="H33" s="60" t="s">
+      <c r="H33" s="57" t="s">
         <v>224</v>
       </c>
       <c r="I33" s="37" t="s">
@@ -4556,13 +4554,13 @@
       </c>
       <c r="L33" s="38"/>
     </row>
-    <row r="34" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="65"/>
-      <c r="B34" s="57">
+    <row r="34" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="62"/>
+      <c r="B34" s="54">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="55" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="36" t="s">
@@ -4592,13 +4590,13 @@
       </c>
       <c r="L34" s="36"/>
     </row>
-    <row r="35" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="65"/>
-      <c r="B35" s="59">
+    <row r="35" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="62"/>
+      <c r="B35" s="56">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="61" t="s">
+      <c r="C35" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="38" t="s">
@@ -4628,13 +4626,13 @@
       </c>
       <c r="L35" s="38"/>
     </row>
-    <row r="36" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="65"/>
-      <c r="B36" s="57">
+    <row r="36" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="62"/>
+      <c r="B36" s="54">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="61" t="s">
+      <c r="C36" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D36" s="36" t="s">
@@ -4664,13 +4662,13 @@
       </c>
       <c r="L36" s="36"/>
     </row>
-    <row r="37" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="65"/>
-      <c r="B37" s="59">
+    <row r="37" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="62"/>
+      <c r="B37" s="56">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D37" s="38" t="s">
@@ -4700,13 +4698,13 @@
       </c>
       <c r="L37" s="38"/>
     </row>
-    <row r="38" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="65"/>
-      <c r="B38" s="57">
+    <row r="38" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="62"/>
+      <c r="B38" s="54">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="36" t="s">
@@ -4736,13 +4734,13 @@
       </c>
       <c r="L38" s="36"/>
     </row>
-    <row r="39" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="65"/>
-      <c r="B39" s="59">
+    <row r="39" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="62"/>
+      <c r="B39" s="56">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="38" t="s">
@@ -4772,13 +4770,13 @@
       </c>
       <c r="L39" s="38"/>
     </row>
-    <row r="40" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="65"/>
-      <c r="B40" s="57">
+    <row r="40" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="62"/>
+      <c r="B40" s="54">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="C40" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="36" t="s">
@@ -4808,13 +4806,13 @@
       </c>
       <c r="L40" s="36"/>
     </row>
-    <row r="41" spans="1:12" s="66" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A41" s="65"/>
-      <c r="B41" s="59">
+    <row r="41" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="62"/>
+      <c r="B41" s="56">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="61" t="s">
+      <c r="C41" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="38" t="s">
@@ -4844,13 +4842,13 @@
       </c>
       <c r="L41" s="38"/>
     </row>
-    <row r="42" spans="1:12" s="66" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A42" s="65"/>
-      <c r="B42" s="57">
+    <row r="42" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="62"/>
+      <c r="B42" s="54">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="58" t="s">
+      <c r="C42" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="36" t="s">
@@ -4880,13 +4878,13 @@
       </c>
       <c r="L42" s="36"/>
     </row>
-    <row r="43" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="65"/>
-      <c r="B43" s="59">
+    <row r="43" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="62"/>
+      <c r="B43" s="56">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D43" s="38" t="s">
@@ -4916,13 +4914,13 @@
       </c>
       <c r="L43" s="38"/>
     </row>
-    <row r="44" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="65"/>
-      <c r="B44" s="57">
+    <row r="44" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="62"/>
+      <c r="B44" s="54">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="61" t="s">
+      <c r="C44" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D44" s="36" t="s">
@@ -4952,13 +4950,13 @@
       </c>
       <c r="L44" s="36"/>
     </row>
-    <row r="45" spans="1:12" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="65"/>
-      <c r="B45" s="59">
+    <row r="45" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="62"/>
+      <c r="B45" s="56">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="58" t="s">
         <v>20</v>
       </c>
       <c r="D45" s="38" t="s">
@@ -4988,13 +4986,13 @@
       </c>
       <c r="L45" s="38"/>
     </row>
-    <row r="46" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A46" s="65"/>
-      <c r="B46" s="57">
+    <row r="46" spans="1:12" s="63" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A46" s="62"/>
+      <c r="B46" s="54">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="58" t="s">
+      <c r="C46" s="55" t="s">
         <v>21</v>
       </c>
       <c r="D46" s="36" t="s">
@@ -5024,13 +5022,13 @@
       </c>
       <c r="L46" s="36"/>
     </row>
-    <row r="47" spans="1:12" s="66" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A47" s="65"/>
-      <c r="B47" s="59">
+    <row r="47" spans="1:12" s="63" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A47" s="62"/>
+      <c r="B47" s="56">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="58" t="s">
         <v>22</v>
       </c>
       <c r="D47" s="38" t="s">
@@ -5060,13 +5058,13 @@
       </c>
       <c r="L47" s="38"/>
     </row>
-    <row r="48" spans="1:12" s="66" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A48" s="65"/>
-      <c r="B48" s="57">
+    <row r="48" spans="1:12" s="63" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A48" s="62"/>
+      <c r="B48" s="54">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="61" t="s">
+      <c r="C48" s="58" t="s">
         <v>22</v>
       </c>
       <c r="D48" s="36" t="s">
@@ -5096,13 +5094,13 @@
       </c>
       <c r="L48" s="36"/>
     </row>
-    <row r="49" spans="1:12" s="66" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A49" s="65"/>
-      <c r="B49" s="59">
+    <row r="49" spans="1:12" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="62"/>
+      <c r="B49" s="56">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="58" t="s">
         <v>19</v>
       </c>
       <c r="D49" s="38" t="s">
@@ -5132,13 +5130,13 @@
       </c>
       <c r="L49" s="38"/>
     </row>
-    <row r="50" spans="1:12" s="66" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A50" s="65"/>
-      <c r="B50" s="57">
+    <row r="50" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A50" s="62"/>
+      <c r="B50" s="54">
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D50" s="36" t="s">
@@ -5168,13 +5166,13 @@
       </c>
       <c r="L50" s="36"/>
     </row>
-    <row r="51" spans="1:12" s="66" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A51" s="65"/>
-      <c r="B51" s="59">
+    <row r="51" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A51" s="62"/>
+      <c r="B51" s="56">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C51" s="58" t="s">
         <v>23</v>
       </c>
       <c r="D51" s="38" t="s">
@@ -5204,13 +5202,13 @@
       </c>
       <c r="L51" s="38"/>
     </row>
-    <row r="52" spans="1:12" s="66" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A52" s="65"/>
-      <c r="B52" s="57">
+    <row r="52" spans="1:12" s="63" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A52" s="62"/>
+      <c r="B52" s="54">
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="55" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="36" t="s">
@@ -5240,13 +5238,13 @@
       </c>
       <c r="L52" s="36"/>
     </row>
-    <row r="53" spans="1:12" s="66" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A53" s="65"/>
-      <c r="B53" s="59">
+    <row r="53" spans="1:12" s="63" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A53" s="62"/>
+      <c r="B53" s="56">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="61" t="s">
+      <c r="C53" s="58" t="s">
         <v>23</v>
       </c>
       <c r="D53" s="38" t="s">
@@ -5276,13 +5274,13 @@
       </c>
       <c r="L53" s="38"/>
     </row>
-    <row r="54" spans="1:12" s="66" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="65"/>
-      <c r="B54" s="57">
+    <row r="54" spans="1:12" s="63" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="62"/>
+      <c r="B54" s="54">
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="C54" s="55" t="s">
         <v>24</v>
       </c>
       <c r="D54" s="36" t="s">
